--- a/customer_service_forms/031_skin_care_consult--customer_service_forms.xlsx
+++ b/customer_service_forms/031_skin_care_consult--customer_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,23 +515,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>skin_care_consult_form</t>
+          <t>skin_type</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>skin_care_form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your skin type?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Select one of the following options - Normal, Dry, Oily, Combination, Sensitive</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,41 +547,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>skin_type</t>
+          <t>skin_condition</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>skin_type</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Describe your skin condition (e.g. acne, aging, etc.)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide details about your skin concerns</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>skin_condition</t>
+          <t>skin_care_products</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>skin_condition</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Are you interested in skin care products?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select one of the following options - Yes, No</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +601,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>skin_care_products</t>
+          <t>followup</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>skin_care_products</t>
+          <t>How often do you follow-up with your skin care products?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +624,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>skin_procedure</t>
+          <t>followup_method</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>skin_procedure</t>
+          <t>How do you follow-up with your skin care products?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +647,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>next_steps</t>
+          <t>skin_care_product_info</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>next_steps</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Please provide detailed information about your skin care products (e.g. name, price, quantity)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide details about your skin care products</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,41 +674,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>skin_care_product_info_price</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>Price of the skin care product</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>followup_frequency</t>
+          <t>skin_care_product_info_price_currency</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>followup_frequency</t>
+          <t>Currency of the skin care product</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +720,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>followup_method</t>
+          <t>skin_care_product_info_weight</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>followup_method</t>
+          <t>Weight of the skin care product</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +743,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>followup_next_steps</t>
+          <t>skin_care_product_info_weight_unit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>followup_next_steps</t>
+          <t>Unit of the skin care product weight</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +766,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>skin_care_product_info</t>
+          <t>skin_care_product_info_size</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>skin_care_product_info</t>
+          <t>Size of the skin care product</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +789,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>skin_care_product_info_additional</t>
+          <t>skin_care_product_info_size_unit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>skin_care_product_info_additional</t>
+          <t>Unit of the skin care product size</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,18 +812,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>skin_care_product_info_price</t>
+          <t>skin_care_product_info_quantity</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>skin_care_product_info_price</t>
+          <t>Quantity of the skin care product</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,271 +835,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>skin_care_product_info_price_currency</t>
+          <t>skin_care_product_info_additional</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>skin_care_product_info_price_currency</t>
+          <t>Additional information about the skin care product</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_price_quantity</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_price_quantity</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_price_unit</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_price_unit</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_weight</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_weight</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_weight_unit</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_weight_unit</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_weight_quantity</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_weight_quantity</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_weight_unit</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_weight_unit</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_size</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_size</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_size_unit</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_size_unit</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_size_quantity</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_size_quantity</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_size_unit</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_size_unit</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_additional</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>skin_care_product_info_additional</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +861,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,68 +889,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>skin_care_products_choices</t>
+          <t>skin_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>skin_care_products_choices</t>
+          <t>skin_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dry</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>followup_frequency_choices</t>
+          <t>skin_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>followup_frequency_choices</t>
+          <t>skin_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Combination</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>skin_type_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sensitive</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>skin_care_products_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>skin_care_products_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>followup_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>followup_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>followup_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>followup_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>followup_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Never</t>
         </is>
       </c>
     </row>
